--- a/nursing/フォーマット/02_訪問看護記録様式/04_訪問看護報告書.xlsx
+++ b/nursing/フォーマット/02_訪問看護記録様式/04_訪問看護報告書.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,8 +28,14 @@
     <font>
       <name val="Meiryo UI"/>
       <b val="1"/>
-      <color rgb="000E7490"/>
-      <sz val="14"/>
+      <color rgb="FF0E7490"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <color rgb="FFDC2626"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Meiryo UI"/>
@@ -43,13 +49,13 @@
     <font>
       <name val="Meiryo UI"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Meiryo UI"/>
       <i val="1"/>
-      <color rgb="006B7280"/>
+      <color rgb="FF6B7280"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -62,17 +68,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CFFAFE"/>
+        <fgColor rgb="FFCFFAFE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000E7490"/>
+        <fgColor rgb="FF0E7490"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8FAFC"/>
+        <fgColor rgb="FFF8FAFC"/>
       </patternFill>
     </fill>
   </fills>
@@ -94,21 +100,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -476,17 +488,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -496,190 +508,259 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
+    <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>【提出義務】毎月、主治医（指示を行った医師）へ提出。精神科訪問看護は別紙様式4を使用。内容は訪問看護計画書に基づき記載。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
           <t>利用者氏名</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>様</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>（様）</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>報告対象月</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">　　年　　月分</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>主治医氏名</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>先生</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>主治医氏名・医療機関名</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>訪問看護ステーション名</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>疾患・傷病名</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>疾患・傷病名（主診断）</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>管理者名</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>訪問看護指示書 有効期限</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　年　月　日まで</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>担当看護師</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>訪問回数・状況</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="25" customHeight="1">
+      <c r="G6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>当月の訪問回数：　　回　 / うち緊急訪問：　　回 / 特別訪問看護指示期間：　なし　あり（　　日〜　　日）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>病状・バイタルサインの経過</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t>【当月訪問実績】</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>訪問回数：　　回　 うち緊急訪問：　　回　 特別訪問看護指示期間：　なし　・　あり（　　日〜　　日）　リハ訪問：　　回（PT/OT/ST）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>・体温：〜℃台　・血圧：/〜/mmHg台　・脈拍：〜回/分台
-・意識レベル：清明 / 傾眠 / その他（　　　　）
-・ADL：（　　）
+          <t>【病状・バイタルサインの経過（月間）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>・体温：　〜　℃台（平均：　　℃）　・血圧：　/　〜　/　mmHg　・脈拍：　〜　回/分　・SpO2：　〜　%
+・意識レベル：清明 / 傾眠傾向 / その他（　　　　　　）
 ・特記すべき病状変化：</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>看護・リハビリの内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>・清拭・入浴介助：　有　無
-・創傷処置：　有（部位：　　）　無
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>【看護・リハビリテーションの内容（月間）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>・清拭・入浴介助：　有（　回）　無
+・創傷・褥瘡処置：　有（部位・状態：　　　　　　）　無
 ・服薬管理・指導：　有　無
-・吸引：　有　無
-・褥瘡処置：　有（部位：　　）　無
+・吸引：　有（　回）　無
+・経管栄養管理：　有　無
+・リハビリ（PT/OT/ST）：　有（内容：　　　　　　　）　無
 ・その他：</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>家族への指導・支援内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>今後の看護・支援の方向性（主治医へ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="50" customHeight="1">
-      <c r="A17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>特記事項・連絡事項</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">報告日：　　年　　月　　日　　担当看護師署名：　　　　　　　　　　管理者確認：　　　　　　　</t>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>【ADL・日常生活状況の変化】</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前月比較：改善（　　） / 不変 / 低下（　　）
+食事：　　　移動：　　　排泄：　　　入浴：　　　意思疎通：　　　</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>【家族への指導・支援内容】</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="50" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>例）体位変換の方法を指導。吸引手技の確認。緊急時対応手順の再確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>【医療機器・医療処置の管理状況】</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>例）人工呼吸器：設定変更なし、作動良好。カテーテル：交換実施（　　日）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>【精神状態・療養意欲・生活面の状況】</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="50" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>例）「体の具合はどうですか」の問いに「まあまあです」と返答あり。外出意欲あり。不安・抑うつなし。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>【今後の看護・支援の方向性（主治医へ）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>例）引き続き現状のケアを継続。次月は通院同行の予定あり。〇〇について主治医の指示を仰ぎたい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>【特記事項・連絡事項（主治医への報告事項）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="50" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>例）〇日に転倒あり（処置済み）。〇日に家族より体調不良の連絡を受け緊急訪問実施。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>報告日：　　年　月　日　　担当看護師署名：　　　　　　　　　　管理者確認署名：　　　　　　　　　（確認日：　年　月　日）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="37">
     <mergeCell ref="A9:H9"/>
+    <mergeCell ref="C6:D6"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A24:H24"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A6:B6"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A16:H16"/>
+    <mergeCell ref="G6:H6"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A23:H23"/>
     <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A22:H22"/>
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A13:H13"/>
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="E3:F3"/>

--- a/nursing/フォーマット/02_訪問看護記録様式/04_訪問看護報告書.xlsx
+++ b/nursing/フォーマット/02_訪問看護記録様式/04_訪問看護報告書.xlsx
@@ -26,37 +26,37 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
       <b val="1"/>
-      <color rgb="FF0E7490"/>
-      <sz val="13"/>
+      <color rgb="00163A2B"/>
+      <sz val="16"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
-      <color rgb="FFDC2626"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
+      <name val="Meiryo"/>
+      <color rgb="005C665C"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <sz val="9"/>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="00163A2B"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="9"/>
+      <name val="Meiryo"/>
+      <color rgb="00283129"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <i val="1"/>
-      <color rgb="FF6B7280"/>
-      <sz val="9"/>
+      <name val="Meiryo"/>
+      <color rgb="005C665C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -68,21 +68,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCFFAFE"/>
+        <fgColor rgb="00E4EFE7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0E7490"/>
+        <fgColor rgb="001F4D3A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8FAFC"/>
+        <fgColor rgb="00F6EDDA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -91,38 +91,60 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <bottom style="medium">
+        <color rgb="00A9854A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DAD3C2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DAD3C2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DAD3C2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DAD3C2"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00A9854A"/>
+      </left>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -486,285 +508,354 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>訪問看護報告書</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>【提出義務】毎月、主治医（指示を行った医師）へ提出。精神科訪問看護は別紙様式4を使用。内容は訪問看護計画書に基づき記載。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>利用者氏名</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>（様）</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+          <t>主治医へ月1回提出。訪問日・病状・看護内容・家庭での療養状況等を報告（別紙様式2に準拠）</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>利用者氏名 / 生年月日</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>報告対象月</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　年　　月分</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>主治医氏名・医療機関名</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>訪問看護ステーション名</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>疾患・傷病名（主診断）</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>管理者名</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　年　　月分</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>訪問看護指示書 有効期限</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　年　月　日まで</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>担当看護師</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>【当月訪問実績】</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>訪問回数：　　回　 うち緊急訪問：　　回　 特別訪問看護指示期間：　なし　・　あり（　　日〜　　日）　リハ訪問：　　回（PT/OT/ST）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>【病状・バイタルサインの経過（月間）】</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>・体温：　〜　℃台（平均：　　℃）　・血圧：　/　〜　/　mmHg　・脈拍：　〜　回/分　・SpO2：　〜　%
-・意識レベル：清明 / 傾眠傾向 / その他（　　　　　　）
-・特記すべき病状変化：</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>【看護・リハビリテーションの内容（月間）】</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="80" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>・清拭・入浴介助：　有（　回）　無
-・創傷・褥瘡処置：　有（部位・状態：　　　　　　）　無
-・服薬管理・指導：　有　無
-・吸引：　有（　回）　無
-・経管栄養管理：　有　無
-・リハビリ（PT/OT/ST）：　有（内容：　　　　　　　）　無
-・その他：</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>【ADL・日常生活状況の変化】</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">前月比較：改善（　　） / 不変 / 低下（　　）
-食事：　　　移動：　　　排泄：　　　入浴：　　　意思疎通：　　　</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>【家族への指導・支援内容】</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="50" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>例）体位変換の方法を指導。吸引手技の確認。緊急時対応手順の再確認。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>【医療機器・医療処置の管理状況】</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>例）人工呼吸器：設定変更なし、作動良好。カテーテル：交換実施（　　日）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>【精神状態・療養意欲・生活面の状況】</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="50" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>例）「体の具合はどうですか」の問いに「まあまあです」と返答あり。外出意欲あり。不安・抑うつなし。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>【今後の看護・支援の方向性（主治医へ）】</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>例）引き続き現状のケアを継続。次月は通院同行の予定あり。〇〇について主治医の指示を仰ぎたい。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>【特記事項・連絡事項（主治医への報告事項）】</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="50" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>例）〇日に転倒あり（処置済み）。〇日に家族より体調不良の連絡を受け緊急訪問実施。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>報告日：　　年　月　日　　担当看護師署名：　　　　　　　　　　管理者確認署名：　　　　　　　　　（確認日：　年　月　日）</t>
-        </is>
-      </c>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>主治医 / 医療機関</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>訪問日（当月）</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>訪問回数 / うち緊急</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="8" customHeight="1"/>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>病状の経過</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="9" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="8" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>看護・リハビリテーションの内容</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="9" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="8" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>家庭での療養状況・介護状況</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="8" customHeight="1"/>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>衛生材料等の使用・特記事項</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="9" t="n"/>
+      <c r="H25" s="9" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>作成者 / 提出日</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="6" t="inlineStr"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>管理者確認</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="6" t="inlineStr"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>※ 主治医の指示書の有効期間内に提供したサービスについて報告。特別管理加算等の対象は処置内容を具体的に記載。</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="n"/>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="11" t="n"/>
+      <c r="G30" s="11" t="n"/>
+      <c r="H30" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="37">
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="C6:D6"/>
+  <mergeCells count="21">
+    <mergeCell ref="A30:H30"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A11:H11"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="C7:H7"/>
+    <mergeCell ref="C28:H28"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A8:B8"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="A29:B29"/>
     <mergeCell ref="A20:H20"/>
+    <mergeCell ref="C5:H5"/>
     <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="C29:H29"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>